--- a/database/HASH11.xlsx
+++ b/database/HASH11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1345"/>
+  <dimension ref="A1:F1346"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27312,19 +27312,39 @@
         <v>46276</v>
       </c>
       <c r="B1345" t="n">
-        <v>51.98</v>
+        <v>51.97999954223633</v>
       </c>
       <c r="C1345" t="n">
-        <v>53.37</v>
+        <v>53.36999893188477</v>
       </c>
       <c r="D1345" t="n">
-        <v>51.49</v>
+        <v>51.4900016784668</v>
       </c>
       <c r="E1345" t="n">
-        <v>51.49</v>
+        <v>51.4900016784668</v>
       </c>
       <c r="F1345" t="n">
         <v>201437</v>
+      </c>
+    </row>
+    <row r="1346">
+      <c r="A1346" s="1" t="n">
+        <v>46279</v>
+      </c>
+      <c r="B1346" t="n">
+        <v>53.05</v>
+      </c>
+      <c r="C1346" t="n">
+        <v>53.25</v>
+      </c>
+      <c r="D1346" t="n">
+        <v>52.25</v>
+      </c>
+      <c r="E1346" t="n">
+        <v>52.25</v>
+      </c>
+      <c r="F1346" t="n">
+        <v>300605</v>
       </c>
     </row>
   </sheetData>

--- a/database/HASH11.xlsx
+++ b/database/HASH11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1346"/>
+  <dimension ref="A1:F1347"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27332,7 +27332,7 @@
         <v>46279</v>
       </c>
       <c r="B1346" t="n">
-        <v>53.05</v>
+        <v>53.04999923706055</v>
       </c>
       <c r="C1346" t="n">
         <v>53.25</v>
@@ -27345,6 +27345,26 @@
       </c>
       <c r="F1346" t="n">
         <v>300605</v>
+      </c>
+    </row>
+    <row r="1347">
+      <c r="A1347" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B1347" t="n">
+        <v>51.03</v>
+      </c>
+      <c r="C1347" t="n">
+        <v>52.03</v>
+      </c>
+      <c r="D1347" t="n">
+        <v>50.55</v>
+      </c>
+      <c r="E1347" t="n">
+        <v>51.8</v>
+      </c>
+      <c r="F1347" t="n">
+        <v>330145</v>
       </c>
     </row>
   </sheetData>

--- a/database/HASH11.xlsx
+++ b/database/HASH11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1347"/>
+  <dimension ref="A1:F1348"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27352,19 +27352,39 @@
         <v>46280</v>
       </c>
       <c r="B1347" t="n">
-        <v>51.03</v>
+        <v>51.02999877929688</v>
       </c>
       <c r="C1347" t="n">
-        <v>52.03</v>
+        <v>52.02999877929688</v>
       </c>
       <c r="D1347" t="n">
-        <v>50.55</v>
+        <v>50.54999923706055</v>
       </c>
       <c r="E1347" t="n">
-        <v>51.8</v>
+        <v>51.79999923706055</v>
       </c>
       <c r="F1347" t="n">
         <v>330145</v>
+      </c>
+    </row>
+    <row r="1348">
+      <c r="A1348" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="B1348" t="n">
+        <v>51</v>
+      </c>
+      <c r="C1348" t="n">
+        <v>51.25</v>
+      </c>
+      <c r="D1348" t="n">
+        <v>50.32</v>
+      </c>
+      <c r="E1348" t="n">
+        <v>51.25</v>
+      </c>
+      <c r="F1348" t="n">
+        <v>129026</v>
       </c>
     </row>
   </sheetData>

--- a/database/HASH11.xlsx
+++ b/database/HASH11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1348"/>
+  <dimension ref="A1:F1349"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27378,13 +27378,33 @@
         <v>51.25</v>
       </c>
       <c r="D1348" t="n">
-        <v>50.32</v>
+        <v>50.31999969482422</v>
       </c>
       <c r="E1348" t="n">
         <v>51.25</v>
       </c>
       <c r="F1348" t="n">
         <v>129026</v>
+      </c>
+    </row>
+    <row r="1349">
+      <c r="A1349" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="B1349" t="n">
+        <v>51.38</v>
+      </c>
+      <c r="C1349" t="n">
+        <v>51.97</v>
+      </c>
+      <c r="D1349" t="n">
+        <v>51.04</v>
+      </c>
+      <c r="E1349" t="n">
+        <v>51.51</v>
+      </c>
+      <c r="F1349" t="n">
+        <v>144563</v>
       </c>
     </row>
   </sheetData>

--- a/database/HASH11.xlsx
+++ b/database/HASH11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1349"/>
+  <dimension ref="A1:F1350"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27391,20 +27391,32 @@
       <c r="A1349" s="1" t="n">
         <v>46282</v>
       </c>
-      <c r="B1349" t="n">
-        <v>51.38</v>
-      </c>
-      <c r="C1349" t="n">
-        <v>51.97</v>
-      </c>
-      <c r="D1349" t="n">
-        <v>51.04</v>
-      </c>
-      <c r="E1349" t="n">
-        <v>51.51</v>
-      </c>
+      <c r="B1349" t="inlineStr"/>
+      <c r="C1349" t="inlineStr"/>
+      <c r="D1349" t="inlineStr"/>
+      <c r="E1349" t="inlineStr"/>
       <c r="F1349" t="n">
-        <v>144563</v>
+        <v>401874</v>
+      </c>
+    </row>
+    <row r="1350">
+      <c r="A1350" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B1350" t="n">
+        <v>54.75</v>
+      </c>
+      <c r="C1350" t="n">
+        <v>55.04</v>
+      </c>
+      <c r="D1350" t="n">
+        <v>52.33</v>
+      </c>
+      <c r="E1350" t="n">
+        <v>52.55</v>
+      </c>
+      <c r="F1350" t="n">
+        <v>405793</v>
       </c>
     </row>
   </sheetData>

--- a/database/HASH11.xlsx
+++ b/database/HASH11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1350"/>
+  <dimension ref="A1:F1351"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27391,12 +27391,20 @@
       <c r="A1349" s="1" t="n">
         <v>46282</v>
       </c>
-      <c r="B1349" t="inlineStr"/>
-      <c r="C1349" t="inlineStr"/>
-      <c r="D1349" t="inlineStr"/>
-      <c r="E1349" t="inlineStr"/>
+      <c r="B1349" t="n">
+        <v>51.38000106811523</v>
+      </c>
+      <c r="C1349" t="n">
+        <v>51.97000122070312</v>
+      </c>
+      <c r="D1349" t="n">
+        <v>51.04000091552734</v>
+      </c>
+      <c r="E1349" t="n">
+        <v>51.5099983215332</v>
+      </c>
       <c r="F1349" t="n">
-        <v>401874</v>
+        <v>144563</v>
       </c>
     </row>
     <row r="1350">
@@ -27407,16 +27415,36 @@
         <v>54.75</v>
       </c>
       <c r="C1350" t="n">
-        <v>55.04</v>
+        <v>55.04000091552734</v>
       </c>
       <c r="D1350" t="n">
-        <v>52.33</v>
+        <v>52.13999938964844</v>
       </c>
       <c r="E1350" t="n">
-        <v>52.55</v>
+        <v>52.54999923706055</v>
       </c>
       <c r="F1350" t="n">
         <v>405793</v>
+      </c>
+    </row>
+    <row r="1351">
+      <c r="A1351" s="1" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B1351" t="n">
+        <v>57.85</v>
+      </c>
+      <c r="C1351" t="n">
+        <v>58.02</v>
+      </c>
+      <c r="D1351" t="n">
+        <v>56.8</v>
+      </c>
+      <c r="E1351" t="n">
+        <v>57.17</v>
+      </c>
+      <c r="F1351" t="n">
+        <v>653218</v>
       </c>
     </row>
   </sheetData>

--- a/database/HASH11.xlsx
+++ b/database/HASH11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1351"/>
+  <dimension ref="A1:F1352"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27432,19 +27432,39 @@
         <v>46286</v>
       </c>
       <c r="B1351" t="n">
-        <v>57.85</v>
+        <v>57.84999847412109</v>
       </c>
       <c r="C1351" t="n">
-        <v>58.02</v>
+        <v>58.02000045776367</v>
       </c>
       <c r="D1351" t="n">
-        <v>56.8</v>
+        <v>56.79999923706055</v>
       </c>
       <c r="E1351" t="n">
-        <v>57.17</v>
+        <v>57.16999816894531</v>
       </c>
       <c r="F1351" t="n">
         <v>653218</v>
+      </c>
+    </row>
+    <row r="1352">
+      <c r="A1352" s="1" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B1352" t="n">
+        <v>57.85</v>
+      </c>
+      <c r="C1352" t="n">
+        <v>58.05</v>
+      </c>
+      <c r="D1352" t="n">
+        <v>57.29</v>
+      </c>
+      <c r="E1352" t="n">
+        <v>57.86</v>
+      </c>
+      <c r="F1352" t="n">
+        <v>264782</v>
       </c>
     </row>
   </sheetData>

--- a/database/HASH11.xlsx
+++ b/database/HASH11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1352"/>
+  <dimension ref="A1:F1353"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27452,19 +27452,39 @@
         <v>46287</v>
       </c>
       <c r="B1352" t="n">
-        <v>57.85</v>
+        <v>57.84999847412109</v>
       </c>
       <c r="C1352" t="n">
-        <v>58.05</v>
+        <v>58.04999923706055</v>
       </c>
       <c r="D1352" t="n">
-        <v>57.29</v>
+        <v>57.29999923706055</v>
       </c>
       <c r="E1352" t="n">
-        <v>57.86</v>
+        <v>57.86000061035156</v>
       </c>
       <c r="F1352" t="n">
         <v>264782</v>
+      </c>
+    </row>
+    <row r="1353">
+      <c r="A1353" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="B1353" t="n">
+        <v>56.95</v>
+      </c>
+      <c r="C1353" t="n">
+        <v>57.78</v>
+      </c>
+      <c r="D1353" t="n">
+        <v>56.24</v>
+      </c>
+      <c r="E1353" t="n">
+        <v>57.65</v>
+      </c>
+      <c r="F1353" t="n">
+        <v>289639</v>
       </c>
     </row>
   </sheetData>

--- a/database/HASH11.xlsx
+++ b/database/HASH11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1353"/>
+  <dimension ref="A1:F1354"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27472,19 +27472,39 @@
         <v>46288</v>
       </c>
       <c r="B1353" t="n">
-        <v>56.95</v>
+        <v>56.95000076293945</v>
       </c>
       <c r="C1353" t="n">
-        <v>57.78</v>
+        <v>57.77999877929688</v>
       </c>
       <c r="D1353" t="n">
-        <v>56.24</v>
+        <v>56.2400016784668</v>
       </c>
       <c r="E1353" t="n">
-        <v>57.65</v>
+        <v>57.65000152587891</v>
       </c>
       <c r="F1353" t="n">
         <v>289639</v>
+      </c>
+    </row>
+    <row r="1354">
+      <c r="A1354" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B1354" t="n">
+        <v>57.47</v>
+      </c>
+      <c r="C1354" t="n">
+        <v>57.57</v>
+      </c>
+      <c r="D1354" t="n">
+        <v>56.55</v>
+      </c>
+      <c r="E1354" t="n">
+        <v>56.7</v>
+      </c>
+      <c r="F1354" t="n">
+        <v>211277</v>
       </c>
     </row>
   </sheetData>

--- a/database/HASH11.xlsx
+++ b/database/HASH11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1354"/>
+  <dimension ref="A1:F1355"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27492,19 +27492,39 @@
         <v>46289</v>
       </c>
       <c r="B1354" t="n">
-        <v>57.47</v>
+        <v>57.47000122070312</v>
       </c>
       <c r="C1354" t="n">
-        <v>57.57</v>
+        <v>57.56999969482422</v>
       </c>
       <c r="D1354" t="n">
-        <v>56.55</v>
+        <v>56.54999923706055</v>
       </c>
       <c r="E1354" t="n">
-        <v>56.7</v>
+        <v>56.70000076293945</v>
       </c>
       <c r="F1354" t="n">
         <v>211277</v>
+      </c>
+    </row>
+    <row r="1355">
+      <c r="A1355" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="B1355" t="n">
+        <v>57.55</v>
+      </c>
+      <c r="C1355" t="n">
+        <v>57.88</v>
+      </c>
+      <c r="D1355" t="n">
+        <v>56.94</v>
+      </c>
+      <c r="E1355" t="n">
+        <v>57.61</v>
+      </c>
+      <c r="F1355" t="n">
+        <v>240994</v>
       </c>
     </row>
   </sheetData>

--- a/database/HASH11.xlsx
+++ b/database/HASH11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1355"/>
+  <dimension ref="A1:F1356"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27512,19 +27512,39 @@
         <v>46290</v>
       </c>
       <c r="B1355" t="n">
-        <v>57.55</v>
+        <v>57.54999923706055</v>
       </c>
       <c r="C1355" t="n">
-        <v>57.88</v>
+        <v>57.88000106811523</v>
       </c>
       <c r="D1355" t="n">
-        <v>56.94</v>
+        <v>56.93999862670898</v>
       </c>
       <c r="E1355" t="n">
-        <v>57.61</v>
+        <v>57.61000061035156</v>
       </c>
       <c r="F1355" t="n">
         <v>240994</v>
+      </c>
+    </row>
+    <row r="1356">
+      <c r="A1356" s="1" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B1356" t="n">
+        <v>57.05</v>
+      </c>
+      <c r="C1356" t="n">
+        <v>57.6</v>
+      </c>
+      <c r="D1356" t="n">
+        <v>56.6</v>
+      </c>
+      <c r="E1356" t="n">
+        <v>57.4</v>
+      </c>
+      <c r="F1356" t="n">
+        <v>138733</v>
       </c>
     </row>
   </sheetData>

--- a/database/HASH11.xlsx
+++ b/database/HASH11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1356"/>
+  <dimension ref="A1:F1357"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27532,19 +27532,39 @@
         <v>46293</v>
       </c>
       <c r="B1356" t="n">
-        <v>57.05</v>
+        <v>57.04999923706055</v>
       </c>
       <c r="C1356" t="n">
-        <v>57.6</v>
+        <v>57.59999847412109</v>
       </c>
       <c r="D1356" t="n">
-        <v>56.6</v>
+        <v>56.70000076293945</v>
       </c>
       <c r="E1356" t="n">
-        <v>57.4</v>
+        <v>57.40000152587891</v>
       </c>
       <c r="F1356" t="n">
         <v>138733</v>
+      </c>
+    </row>
+    <row r="1357">
+      <c r="A1357" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="B1357" t="n">
+        <v>57</v>
+      </c>
+      <c r="C1357" t="n">
+        <v>57.98</v>
+      </c>
+      <c r="D1357" t="n">
+        <v>57</v>
+      </c>
+      <c r="E1357" t="n">
+        <v>57.68</v>
+      </c>
+      <c r="F1357" t="n">
+        <v>111991</v>
       </c>
     </row>
   </sheetData>

--- a/database/HASH11.xlsx
+++ b/database/HASH11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1357"/>
+  <dimension ref="A1:F1358"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27555,16 +27555,36 @@
         <v>57</v>
       </c>
       <c r="C1357" t="n">
-        <v>57.98</v>
+        <v>57.97999954223633</v>
       </c>
       <c r="D1357" t="n">
         <v>57</v>
       </c>
       <c r="E1357" t="n">
-        <v>57.68</v>
+        <v>57.68000030517578</v>
       </c>
       <c r="F1357" t="n">
         <v>111991</v>
+      </c>
+    </row>
+    <row r="1358">
+      <c r="A1358" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B1358" t="n">
+        <v>56.93</v>
+      </c>
+      <c r="C1358" t="n">
+        <v>57.98</v>
+      </c>
+      <c r="D1358" t="n">
+        <v>56.57</v>
+      </c>
+      <c r="E1358" t="n">
+        <v>57.76</v>
+      </c>
+      <c r="F1358" t="n">
+        <v>177676</v>
       </c>
     </row>
   </sheetData>

--- a/database/HASH11.xlsx
+++ b/database/HASH11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1358"/>
+  <dimension ref="A1:F1359"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27572,19 +27572,39 @@
         <v>46295</v>
       </c>
       <c r="B1358" t="n">
-        <v>56.93</v>
+        <v>56.93000030517578</v>
       </c>
       <c r="C1358" t="n">
-        <v>57.98</v>
+        <v>57.97999954223633</v>
       </c>
       <c r="D1358" t="n">
-        <v>56.57</v>
+        <v>56.56999969482422</v>
       </c>
       <c r="E1358" t="n">
-        <v>57.76</v>
+        <v>57.7599983215332</v>
       </c>
       <c r="F1358" t="n">
         <v>177676</v>
+      </c>
+    </row>
+    <row r="1359">
+      <c r="A1359" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B1359" t="n">
+        <v>58.05</v>
+      </c>
+      <c r="C1359" t="n">
+        <v>58.27</v>
+      </c>
+      <c r="D1359" t="n">
+        <v>56.84</v>
+      </c>
+      <c r="E1359" t="n">
+        <v>57.47</v>
+      </c>
+      <c r="F1359" t="n">
+        <v>166944</v>
       </c>
     </row>
   </sheetData>

--- a/database/HASH11.xlsx
+++ b/database/HASH11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1359"/>
+  <dimension ref="A1:F1360"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27592,19 +27592,39 @@
         <v>46296</v>
       </c>
       <c r="B1359" t="n">
-        <v>58.05</v>
+        <v>58.04000091552734</v>
       </c>
       <c r="C1359" t="n">
-        <v>58.27</v>
+        <v>58.27000045776367</v>
       </c>
       <c r="D1359" t="n">
-        <v>56.84</v>
+        <v>56.56999969482422</v>
       </c>
       <c r="E1359" t="n">
-        <v>57.47</v>
+        <v>57.7599983215332</v>
       </c>
       <c r="F1359" t="n">
         <v>166944</v>
+      </c>
+    </row>
+    <row r="1360">
+      <c r="A1360" s="1" t="n">
+        <v>46297</v>
+      </c>
+      <c r="B1360" t="n">
+        <v>57.72</v>
+      </c>
+      <c r="C1360" t="n">
+        <v>59.64</v>
+      </c>
+      <c r="D1360" t="n">
+        <v>57.55</v>
+      </c>
+      <c r="E1360" t="n">
+        <v>59.11</v>
+      </c>
+      <c r="F1360" t="n">
+        <v>256913</v>
       </c>
     </row>
   </sheetData>

--- a/database/HASH11.xlsx
+++ b/database/HASH11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1360"/>
+  <dimension ref="A1:F1361"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27612,19 +27612,39 @@
         <v>46297</v>
       </c>
       <c r="B1360" t="n">
-        <v>57.72</v>
+        <v>57.72000122070312</v>
       </c>
       <c r="C1360" t="n">
-        <v>59.64</v>
+        <v>59.63999938964844</v>
       </c>
       <c r="D1360" t="n">
-        <v>57.55</v>
+        <v>57.54999923706055</v>
       </c>
       <c r="E1360" t="n">
-        <v>59.11</v>
+        <v>59.11000061035156</v>
       </c>
       <c r="F1360" t="n">
         <v>256913</v>
+      </c>
+    </row>
+    <row r="1361">
+      <c r="A1361" s="1" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B1361" t="n">
+        <v>55.55</v>
+      </c>
+      <c r="C1361" t="n">
+        <v>56.87</v>
+      </c>
+      <c r="D1361" t="n">
+        <v>51.99</v>
+      </c>
+      <c r="E1361" t="n">
+        <v>56.45</v>
+      </c>
+      <c r="F1361" t="n">
+        <v>406671</v>
       </c>
     </row>
   </sheetData>

--- a/database/HASH11.xlsx
+++ b/database/HASH11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1361"/>
+  <dimension ref="A1:F1362"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27632,19 +27632,39 @@
         <v>46300</v>
       </c>
       <c r="B1361" t="n">
-        <v>55.55</v>
+        <v>55.54999923706055</v>
       </c>
       <c r="C1361" t="n">
-        <v>56.87</v>
+        <v>56.86999893188477</v>
       </c>
       <c r="D1361" t="n">
-        <v>51.99</v>
+        <v>51.9900016784668</v>
       </c>
       <c r="E1361" t="n">
-        <v>56.45</v>
+        <v>56.45000076293945</v>
       </c>
       <c r="F1361" t="n">
         <v>406671</v>
+      </c>
+    </row>
+    <row r="1362">
+      <c r="A1362" s="1" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B1362" t="n">
+        <v>55.9</v>
+      </c>
+      <c r="C1362" t="n">
+        <v>56.66</v>
+      </c>
+      <c r="D1362" t="n">
+        <v>55.71</v>
+      </c>
+      <c r="E1362" t="n">
+        <v>55.71</v>
+      </c>
+      <c r="F1362" t="n">
+        <v>167497</v>
       </c>
     </row>
   </sheetData>

--- a/database/HASH11.xlsx
+++ b/database/HASH11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1362"/>
+  <dimension ref="A1:F1363"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27652,19 +27652,39 @@
         <v>46301</v>
       </c>
       <c r="B1362" t="n">
-        <v>55.9</v>
+        <v>55.90000152587891</v>
       </c>
       <c r="C1362" t="n">
-        <v>56.66</v>
+        <v>56.65999984741211</v>
       </c>
       <c r="D1362" t="n">
-        <v>55.71</v>
+        <v>55.70999908447266</v>
       </c>
       <c r="E1362" t="n">
-        <v>55.71</v>
+        <v>55.70999908447266</v>
       </c>
       <c r="F1362" t="n">
         <v>167497</v>
+      </c>
+    </row>
+    <row r="1363">
+      <c r="A1363" s="1" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B1363" t="n">
+        <v>54.52</v>
+      </c>
+      <c r="C1363" t="n">
+        <v>54.96</v>
+      </c>
+      <c r="D1363" t="n">
+        <v>54.33</v>
+      </c>
+      <c r="E1363" t="n">
+        <v>54.8</v>
+      </c>
+      <c r="F1363" t="n">
+        <v>189687</v>
       </c>
     </row>
   </sheetData>

--- a/database/HASH11.xlsx
+++ b/database/HASH11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1363"/>
+  <dimension ref="A1:F1364"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27672,19 +27672,39 @@
         <v>46302</v>
       </c>
       <c r="B1363" t="n">
-        <v>54.52</v>
+        <v>54.52000045776367</v>
       </c>
       <c r="C1363" t="n">
-        <v>54.96</v>
+        <v>54.95999908447266</v>
       </c>
       <c r="D1363" t="n">
-        <v>54.33</v>
+        <v>54.33000183105469</v>
       </c>
       <c r="E1363" t="n">
-        <v>54.8</v>
+        <v>54.79999923706055</v>
       </c>
       <c r="F1363" t="n">
         <v>189687</v>
+      </c>
+    </row>
+    <row r="1364">
+      <c r="A1364" s="1" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B1364" t="n">
+        <v>53.15</v>
+      </c>
+      <c r="C1364" t="n">
+        <v>54.24</v>
+      </c>
+      <c r="D1364" t="n">
+        <v>52.31</v>
+      </c>
+      <c r="E1364" t="n">
+        <v>53.93</v>
+      </c>
+      <c r="F1364" t="n">
+        <v>367841</v>
       </c>
     </row>
   </sheetData>

--- a/database/HASH11.xlsx
+++ b/database/HASH11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1364"/>
+  <dimension ref="A1:F1365"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27692,19 +27692,39 @@
         <v>46303</v>
       </c>
       <c r="B1364" t="n">
-        <v>53.15</v>
+        <v>53.15000152587891</v>
       </c>
       <c r="C1364" t="n">
-        <v>54.24</v>
+        <v>54.2400016784668</v>
       </c>
       <c r="D1364" t="n">
-        <v>52.31</v>
+        <v>52.31999969482422</v>
       </c>
       <c r="E1364" t="n">
-        <v>53.93</v>
+        <v>53.93000030517578</v>
       </c>
       <c r="F1364" t="n">
         <v>367841</v>
+      </c>
+    </row>
+    <row r="1365">
+      <c r="A1365" s="1" t="n">
+        <v>46304</v>
+      </c>
+      <c r="B1365" t="n">
+        <v>53.4</v>
+      </c>
+      <c r="C1365" t="n">
+        <v>54</v>
+      </c>
+      <c r="D1365" t="n">
+        <v>53.15</v>
+      </c>
+      <c r="E1365" t="n">
+        <v>53.69</v>
+      </c>
+      <c r="F1365" t="n">
+        <v>126773</v>
       </c>
     </row>
   </sheetData>

--- a/database/HASH11.xlsx
+++ b/database/HASH11.xlsx
@@ -27712,16 +27712,16 @@
         <v>46304</v>
       </c>
       <c r="B1365" t="n">
-        <v>53.4</v>
+        <v>53.40000152587891</v>
       </c>
       <c r="C1365" t="n">
         <v>54</v>
       </c>
       <c r="D1365" t="n">
-        <v>53.15</v>
+        <v>53.15000152587891</v>
       </c>
       <c r="E1365" t="n">
-        <v>53.69</v>
+        <v>53.68999862670898</v>
       </c>
       <c r="F1365" t="n">
         <v>126773</v>

--- a/database/HASH11.xlsx
+++ b/database/HASH11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1365"/>
+  <dimension ref="A1:F1366"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27727,6 +27727,26 @@
         <v>126773</v>
       </c>
     </row>
+    <row r="1366">
+      <c r="A1366" s="1" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B1366" t="n">
+        <v>53.91</v>
+      </c>
+      <c r="C1366" t="n">
+        <v>54.23</v>
+      </c>
+      <c r="D1366" t="n">
+        <v>53.65</v>
+      </c>
+      <c r="E1366" t="n">
+        <v>53.8</v>
+      </c>
+      <c r="F1366" t="n">
+        <v>149960</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/database/HASH11.xlsx
+++ b/database/HASH11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1366"/>
+  <dimension ref="A1:F1367"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27732,19 +27732,39 @@
         <v>46308</v>
       </c>
       <c r="B1366" t="n">
-        <v>53.91</v>
+        <v>53.90999984741211</v>
       </c>
       <c r="C1366" t="n">
-        <v>54.23</v>
+        <v>54.22999954223633</v>
       </c>
       <c r="D1366" t="n">
-        <v>53.65</v>
+        <v>53.65000152587891</v>
       </c>
       <c r="E1366" t="n">
-        <v>53.8</v>
+        <v>53.79999923706055</v>
       </c>
       <c r="F1366" t="n">
         <v>149960</v>
+      </c>
+    </row>
+    <row r="1367">
+      <c r="A1367" s="1" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B1367" t="n">
+        <v>53.07</v>
+      </c>
+      <c r="C1367" t="n">
+        <v>53.9</v>
+      </c>
+      <c r="D1367" t="n">
+        <v>52.59</v>
+      </c>
+      <c r="E1367" t="n">
+        <v>53.9</v>
+      </c>
+      <c r="F1367" t="n">
+        <v>179205</v>
       </c>
     </row>
   </sheetData>

--- a/database/HASH11.xlsx
+++ b/database/HASH11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1367"/>
+  <dimension ref="A1:F1368"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27752,19 +27752,39 @@
         <v>46309</v>
       </c>
       <c r="B1367" t="n">
-        <v>53.07</v>
+        <v>53.06999969482422</v>
       </c>
       <c r="C1367" t="n">
-        <v>53.9</v>
+        <v>53.90000152587891</v>
       </c>
       <c r="D1367" t="n">
-        <v>52.59</v>
+        <v>52.59000015258789</v>
       </c>
       <c r="E1367" t="n">
-        <v>53.9</v>
+        <v>53.90000152587891</v>
       </c>
       <c r="F1367" t="n">
         <v>179205</v>
+      </c>
+    </row>
+    <row r="1368">
+      <c r="A1368" s="1" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B1368" t="n">
+        <v>54.29</v>
+      </c>
+      <c r="C1368" t="n">
+        <v>54.29</v>
+      </c>
+      <c r="D1368" t="n">
+        <v>51.86</v>
+      </c>
+      <c r="E1368" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="F1368" t="n">
+        <v>270979</v>
       </c>
     </row>
   </sheetData>

--- a/database/HASH11.xlsx
+++ b/database/HASH11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1368"/>
+  <dimension ref="A1:F1369"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27772,19 +27772,39 @@
         <v>46310</v>
       </c>
       <c r="B1368" t="n">
-        <v>54.29</v>
+        <v>54.29000091552734</v>
       </c>
       <c r="C1368" t="n">
-        <v>54.29</v>
+        <v>54.29000091552734</v>
       </c>
       <c r="D1368" t="n">
-        <v>51.86</v>
+        <v>51.93999862670898</v>
       </c>
       <c r="E1368" t="n">
         <v>52.5</v>
       </c>
       <c r="F1368" t="n">
         <v>270979</v>
+      </c>
+    </row>
+    <row r="1369">
+      <c r="A1369" s="1" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B1369" t="n">
+        <v>53.24</v>
+      </c>
+      <c r="C1369" t="n">
+        <v>54.18</v>
+      </c>
+      <c r="D1369" t="n">
+        <v>52.86</v>
+      </c>
+      <c r="E1369" t="n">
+        <v>54</v>
+      </c>
+      <c r="F1369" t="n">
+        <v>130622</v>
       </c>
     </row>
   </sheetData>

--- a/database/HASH11.xlsx
+++ b/database/HASH11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1369"/>
+  <dimension ref="A1:F1370"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27792,19 +27792,39 @@
         <v>46311</v>
       </c>
       <c r="B1369" t="n">
-        <v>53.24</v>
+        <v>53.2400016784668</v>
       </c>
       <c r="C1369" t="n">
-        <v>54.18</v>
+        <v>54.18000030517578</v>
       </c>
       <c r="D1369" t="n">
-        <v>52.86</v>
+        <v>52.88999938964844</v>
       </c>
       <c r="E1369" t="n">
         <v>54</v>
       </c>
       <c r="F1369" t="n">
         <v>130622</v>
+      </c>
+    </row>
+    <row r="1370">
+      <c r="A1370" s="1" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B1370" t="n">
+        <v>52.94</v>
+      </c>
+      <c r="C1370" t="n">
+        <v>54</v>
+      </c>
+      <c r="D1370" t="n">
+        <v>52.8</v>
+      </c>
+      <c r="E1370" t="n">
+        <v>53.5</v>
+      </c>
+      <c r="F1370" t="n">
+        <v>89161</v>
       </c>
     </row>
   </sheetData>

--- a/database/HASH11.xlsx
+++ b/database/HASH11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1370"/>
+  <dimension ref="A1:F1371"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27812,19 +27812,39 @@
         <v>46314</v>
       </c>
       <c r="B1370" t="n">
-        <v>52.94</v>
+        <v>52.93999862670898</v>
       </c>
       <c r="C1370" t="n">
         <v>54</v>
       </c>
       <c r="D1370" t="n">
-        <v>52.8</v>
+        <v>52.79999923706055</v>
       </c>
       <c r="E1370" t="n">
         <v>53.5</v>
       </c>
       <c r="F1370" t="n">
         <v>89161</v>
+      </c>
+    </row>
+    <row r="1371">
+      <c r="A1371" s="1" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B1371" t="n">
+        <v>53.07</v>
+      </c>
+      <c r="C1371" t="n">
+        <v>53.75</v>
+      </c>
+      <c r="D1371" t="n">
+        <v>52.41</v>
+      </c>
+      <c r="E1371" t="n">
+        <v>52.63</v>
+      </c>
+      <c r="F1371" t="n">
+        <v>98051</v>
       </c>
     </row>
   </sheetData>

--- a/database/HASH11.xlsx
+++ b/database/HASH11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1371"/>
+  <dimension ref="A1:F1372"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27832,19 +27832,39 @@
         <v>46315</v>
       </c>
       <c r="B1371" t="n">
-        <v>53.07</v>
+        <v>53.06999969482422</v>
       </c>
       <c r="C1371" t="n">
         <v>53.75</v>
       </c>
       <c r="D1371" t="n">
-        <v>52.41</v>
+        <v>52.40999984741211</v>
       </c>
       <c r="E1371" t="n">
-        <v>52.63</v>
+        <v>52.63000106811523</v>
       </c>
       <c r="F1371" t="n">
         <v>98051</v>
+      </c>
+    </row>
+    <row r="1372">
+      <c r="A1372" s="1" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B1372" t="n">
+        <v>54.61</v>
+      </c>
+      <c r="C1372" t="n">
+        <v>54.76</v>
+      </c>
+      <c r="D1372" t="n">
+        <v>53.47</v>
+      </c>
+      <c r="E1372" t="n">
+        <v>53.83</v>
+      </c>
+      <c r="F1372" t="n">
+        <v>349578</v>
       </c>
     </row>
   </sheetData>

--- a/database/HASH11.xlsx
+++ b/database/HASH11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1372"/>
+  <dimension ref="A1:F1373"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27852,19 +27852,39 @@
         <v>46316</v>
       </c>
       <c r="B1372" t="n">
-        <v>54.61</v>
+        <v>54.61000061035156</v>
       </c>
       <c r="C1372" t="n">
-        <v>54.76</v>
+        <v>54.7599983215332</v>
       </c>
       <c r="D1372" t="n">
-        <v>53.47</v>
+        <v>53.47000122070312</v>
       </c>
       <c r="E1372" t="n">
-        <v>53.83</v>
+        <v>53.83000183105469</v>
       </c>
       <c r="F1372" t="n">
         <v>349578</v>
+      </c>
+    </row>
+    <row r="1373">
+      <c r="A1373" s="1" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B1373" t="n">
+        <v>52.65</v>
+      </c>
+      <c r="C1373" t="n">
+        <v>53.23</v>
+      </c>
+      <c r="D1373" t="n">
+        <v>52.25</v>
+      </c>
+      <c r="E1373" t="n">
+        <v>52.95</v>
+      </c>
+      <c r="F1373" t="n">
+        <v>224352</v>
       </c>
     </row>
   </sheetData>

--- a/database/HASH11.xlsx
+++ b/database/HASH11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1373"/>
+  <dimension ref="A1:F1374"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27872,19 +27872,39 @@
         <v>46317</v>
       </c>
       <c r="B1373" t="n">
-        <v>52.65</v>
+        <v>52.65000152587891</v>
       </c>
       <c r="C1373" t="n">
-        <v>53.23</v>
+        <v>53.22999954223633</v>
       </c>
       <c r="D1373" t="n">
         <v>52.25</v>
       </c>
       <c r="E1373" t="n">
-        <v>52.95</v>
+        <v>52.95000076293945</v>
       </c>
       <c r="F1373" t="n">
         <v>224352</v>
+      </c>
+    </row>
+    <row r="1374">
+      <c r="A1374" s="1" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B1374" t="n">
+        <v>52</v>
+      </c>
+      <c r="C1374" t="n">
+        <v>52.98</v>
+      </c>
+      <c r="D1374" t="n">
+        <v>51.86</v>
+      </c>
+      <c r="E1374" t="n">
+        <v>52.7</v>
+      </c>
+      <c r="F1374" t="n">
+        <v>183438</v>
       </c>
     </row>
   </sheetData>

--- a/database/HASH11.xlsx
+++ b/database/HASH11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1374"/>
+  <dimension ref="A1:F1375"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27895,16 +27895,36 @@
         <v>52</v>
       </c>
       <c r="C1374" t="n">
-        <v>52.98</v>
+        <v>52.97999954223633</v>
       </c>
       <c r="D1374" t="n">
-        <v>51.86</v>
+        <v>51.86000061035156</v>
       </c>
       <c r="E1374" t="n">
-        <v>52.7</v>
+        <v>52.70000076293945</v>
       </c>
       <c r="F1374" t="n">
         <v>183438</v>
+      </c>
+    </row>
+    <row r="1375">
+      <c r="A1375" s="1" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B1375" t="n">
+        <v>54.72</v>
+      </c>
+      <c r="C1375" t="n">
+        <v>56.22</v>
+      </c>
+      <c r="D1375" t="n">
+        <v>53.04</v>
+      </c>
+      <c r="E1375" t="n">
+        <v>54.72</v>
+      </c>
+      <c r="F1375" t="n">
+        <v>713757</v>
       </c>
     </row>
   </sheetData>

--- a/database/HASH11.xlsx
+++ b/database/HASH11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1375"/>
+  <dimension ref="A1:F1376"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27912,19 +27912,39 @@
         <v>46321</v>
       </c>
       <c r="B1375" t="n">
-        <v>54.72</v>
+        <v>54.72000122070312</v>
       </c>
       <c r="C1375" t="n">
-        <v>56.22</v>
+        <v>56.22000122070312</v>
       </c>
       <c r="D1375" t="n">
-        <v>53.04</v>
+        <v>53.04000091552734</v>
       </c>
       <c r="E1375" t="n">
-        <v>54.72</v>
+        <v>53.79999923706055</v>
       </c>
       <c r="F1375" t="n">
-        <v>713757</v>
+        <v>719368</v>
+      </c>
+    </row>
+    <row r="1376">
+      <c r="A1376" s="1" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B1376" t="n">
+        <v>54.9</v>
+      </c>
+      <c r="C1376" t="n">
+        <v>55.11</v>
+      </c>
+      <c r="D1376" t="n">
+        <v>53.91</v>
+      </c>
+      <c r="E1376" t="n">
+        <v>54.7</v>
+      </c>
+      <c r="F1376" t="n">
+        <v>533606</v>
       </c>
     </row>
   </sheetData>

--- a/database/HASH11.xlsx
+++ b/database/HASH11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1376"/>
+  <dimension ref="A1:F1377"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27932,19 +27932,39 @@
         <v>46322</v>
       </c>
       <c r="B1376" t="n">
-        <v>54.9</v>
+        <v>54.90000152587891</v>
       </c>
       <c r="C1376" t="n">
-        <v>55.11</v>
+        <v>55.09999847412109</v>
       </c>
       <c r="D1376" t="n">
-        <v>53.91</v>
+        <v>53.90999984741211</v>
       </c>
       <c r="E1376" t="n">
-        <v>54.7</v>
+        <v>54.70000076293945</v>
       </c>
       <c r="F1376" t="n">
         <v>533606</v>
+      </c>
+    </row>
+    <row r="1377">
+      <c r="A1377" s="1" t="n">
+        <v>46323</v>
+      </c>
+      <c r="B1377" t="n">
+        <v>55.73</v>
+      </c>
+      <c r="C1377" t="n">
+        <v>55.9</v>
+      </c>
+      <c r="D1377" t="n">
+        <v>54.56</v>
+      </c>
+      <c r="E1377" t="n">
+        <v>54.61</v>
+      </c>
+      <c r="F1377" t="n">
+        <v>353583</v>
       </c>
     </row>
   </sheetData>

--- a/database/HASH11.xlsx
+++ b/database/HASH11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1377"/>
+  <dimension ref="A1:F1378"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27952,19 +27952,39 @@
         <v>46323</v>
       </c>
       <c r="B1377" t="n">
-        <v>55.73</v>
+        <v>55.72999954223633</v>
       </c>
       <c r="C1377" t="n">
-        <v>55.9</v>
+        <v>55.90000152587891</v>
       </c>
       <c r="D1377" t="n">
-        <v>54.56</v>
+        <v>54.56000137329102</v>
       </c>
       <c r="E1377" t="n">
-        <v>54.61</v>
+        <v>54.61000061035156</v>
       </c>
       <c r="F1377" t="n">
         <v>353583</v>
+      </c>
+    </row>
+    <row r="1378">
+      <c r="A1378" s="1" t="n">
+        <v>46324</v>
+      </c>
+      <c r="B1378" t="n">
+        <v>55.68</v>
+      </c>
+      <c r="C1378" t="n">
+        <v>56.91</v>
+      </c>
+      <c r="D1378" t="n">
+        <v>54.75</v>
+      </c>
+      <c r="E1378" t="n">
+        <v>55.45</v>
+      </c>
+      <c r="F1378" t="n">
+        <v>298254</v>
       </c>
     </row>
   </sheetData>

--- a/database/HASH11.xlsx
+++ b/database/HASH11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1378"/>
+  <dimension ref="A1:F1379"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27972,19 +27972,39 @@
         <v>46324</v>
       </c>
       <c r="B1378" t="n">
-        <v>55.68</v>
+        <v>55.68000030517578</v>
       </c>
       <c r="C1378" t="n">
-        <v>56.91</v>
+        <v>56.90000152587891</v>
       </c>
       <c r="D1378" t="n">
         <v>54.75</v>
       </c>
       <c r="E1378" t="n">
-        <v>55.45</v>
+        <v>55.45000076293945</v>
       </c>
       <c r="F1378" t="n">
         <v>298254</v>
+      </c>
+    </row>
+    <row r="1379">
+      <c r="A1379" s="1" t="n">
+        <v>46325</v>
+      </c>
+      <c r="B1379" t="n">
+        <v>53.81</v>
+      </c>
+      <c r="C1379" t="n">
+        <v>54.49</v>
+      </c>
+      <c r="D1379" t="n">
+        <v>53.34</v>
+      </c>
+      <c r="E1379" t="n">
+        <v>54.44</v>
+      </c>
+      <c r="F1379" t="n">
+        <v>240153</v>
       </c>
     </row>
   </sheetData>
